--- a/Final.xlsx
+++ b/Final.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\libs\MetaSklearn_examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\thieu\github\MetaSklearn_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E930FE2A-A685-4479-A4E9-E137951420C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D2E851D2-1D7B-403D-B65F-5AF9867CF94B}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="80">
   <si>
     <t>GridSearchCV</t>
   </si>
@@ -113,12 +113,179 @@
   </si>
   <si>
     <t>SVM</t>
+  </si>
+  <si>
+    <t>BayesSearchCV</t>
+  </si>
+  <si>
+    <t>RW-GWO (MetaSearchCV)</t>
+  </si>
+  <si>
+    <t>INFO (MetaSearchCV)</t>
+  </si>
+  <si>
+    <t>SHADE (MetaSearchCV)</t>
+  </si>
+  <si>
+    <t>ARO (MetaSearchCV)</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>{'C': 50.0, 'coef0': 0.0, 'gamma': 'scale', 'kernel': 'linear'}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(50.171157044742145), 'coef0': np.float64(0.39882444244455306), 'gamma': 'scale', 'kernel': 'linear'}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'C': 49.99999999999999, 'coef0': 0.0, 'gamma': 'auto', 'kernel': 'linear'})</t>
+  </si>
+  <si>
+    <t>{'C': 35.76127659433002, 'kernel': 'linear', 'gamma': 1e-05, 'coef0': 0.5648627160776923}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(48.30014800830839), 'kernel': 'linear', 'gamma': 0.001, 'coef0': np.float64(0.7475741230731562)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(43.25431090348414), 'kernel': 'linear', 'gamma': 1e-05, 'coef0': np.float64(0.6537113970847385)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(43.19376528793036), 'kernel': 'linear', 'gamma': 1e-05, 'coef0': np.float64(0.9588778864884591)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(42.21455605620268), 'kernel': 'linear', 'gamma': 1e-05, 'coef0': np.float64(0.0)}</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 70}</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': 7, 'max_features': 0.15, 'min_samples_leaf': 4, 'min_samples_split': 7, 'n_estimators': 121}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'criterion': 'gini', 'max_depth': 7, 'max_features': 0.25, 'min_samples_leaf': 3, 'min_samples_split': 8, 'n_estimators': 91})</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 102, 'criterion': 'gini', 'max_depth': 6, 'min_samples_split': 8, 'min_samples_leaf': 5, 'max_features': 3}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(50), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(5), 'min_samples_leaf': np.int64(5), 'max_features': 3}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(150), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(5), 'min_samples_leaf': np.int64(5), 'max_features': 'log2'}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(50), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(2), 'min_samples_leaf': np.int64(1), 'max_features': 0.15}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(69), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(2), 'min_samples_leaf': np.int64(2), 'max_features': 0.15}</t>
+  </si>
+  <si>
+    <t>{'activation': 'identity', 'alpha': 0.01, 'batch_size': 32, 'hidden_layer_sizes': (30, 10), 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'solver': 'lbfgs'}</t>
+  </si>
+  <si>
+    <t>{'activation': 'identity', 'alpha': np.float64(0.0949889027981886), 'batch_size': 64, 'hidden_layer_sizes': (30, 10), 'learning_rate': 'invscaling', 'learning_rate_init': np.float64(0.03801587002554444), 'solver': 'lbfgs'}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'activation': 'identity', 'alpha': 0.030794009012538082, 'batch_size': 32, 'hidden_layer_sizes': 40, 'learning_rate': 'invscaling', 'learning_rate_init': 0.001, 'solver': 'lbfgs'})</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (40,), 'activation': 'identity', 'solver': 'lbfgs', 'alpha': 0.02768775666220038, 'batch_size': 64, 'learning_rate': 'adaptive', 'learning_rate_init': 0.006121322745465948}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (30, 10), 'activation': 'identity', 'solver': 'lbfgs', 'alpha': np.float64(0.006272711552676152), 'batch_size': 32, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.01047471255631352)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (30,), 'activation': 'identity', 'solver': 'lbfgs', 'alpha': np.float64(0.0010085625479903763), 'batch_size': 128, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.0014229655176268576)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (40,), 'activation': 'identity', 'solver': 'lbfgs', 'alpha': np.float64(0.02271742353627687), 'batch_size': 32, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.0010000615960330768)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (30,), 'activation': 'identity', 'solver': 'lbfgs', 'alpha': np.float64(0.0011115189807713933), 'batch_size': 32, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.0013296068690786345)}</t>
+  </si>
+  <si>
+    <t>{'C': 10.0, 'coef0': 1.0, 'gamma': 'scale', 'kernel': 'poly'}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(7.168573438476171), 'coef0': np.float64(0.7290071680409873), 'gamma': 'scale', 'kernel': 'rbf'}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'C': 10.0, 'coef0': 0.6898025104052534, 'gamma': 'scale', 'kernel': 'poly'})</t>
+  </si>
+  <si>
+    <t>{'C': 9.875030659592984, 'kernel': 'rbf', 'gamma': 'scale', 'coef0': 0.9988782421189562}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(9.28204741884648), 'kernel': 'poly', 'gamma': 'scale', 'coef0': np.float64(0.9858603008276501)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(9.9993004570298), 'kernel': 'poly', 'gamma': 'scale', 'coef0': np.float64(0.9999748774054859)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(9.290840398965733), 'kernel': 'poly', 'gamma': 'scale', 'coef0': np.float64(1.0)}</t>
+  </si>
+  <si>
+    <t>{'C': np.float64(9.080551228132128), 'kernel': 'poly', 'gamma': 'scale', 'coef0': np.float64(1.0)}</t>
+  </si>
+  <si>
+    <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 4, 'min_samples_leaf': 1, 'min_samples_split': 3, 'n_estimators': 40}</t>
+  </si>
+  <si>
+    <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 4, 'min_samples_leaf': 1, 'min_samples_split': 3, 'n_estimators': 27}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'criterion': 'entropy', 'max_depth': 6, 'max_features': 3, 'min_samples_leaf': 2, 'min_samples_split': 3, 'n_estimators': 54})</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 30, 'criterion': 'entropy', 'max_depth': 6, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 3}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(36), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(3), 'min_samples_leaf': np.int64(1), 'max_features': 3}</t>
+  </si>
+  <si>
+    <t>{'n_estimators': np.int64(22), 'criterion': 'entropy', 'max_depth': None, 'min_samples_split': np.int64(3), 'min_samples_leaf': np.int64(1), 'max_features': 3}</t>
+  </si>
+  <si>
+    <t>{'activation': 'logistic', 'alpha': 0.001, 'batch_size': 8, 'hidden_layer_sizes': (25,), 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'solver': 'lbfgs'}</t>
+  </si>
+  <si>
+    <t>{'activation': 'tanh', 'alpha': np.float64(0.04093475643167195), 'batch_size': 32, 'hidden_layer_sizes': (15,), 'learning_rate': 'constant', 'learning_rate_init': np.float64(0.0056450412719997725), 'solver': 'lbfgs'}</t>
+  </si>
+  <si>
+    <t>OrderedDict({'activation': 'logistic', 'alpha': 0.0019955258191031496, 'batch_size': 8, 'hidden_layer_sizes': 50, 'learning_rate': 'invscaling', 'learning_rate_init': 0.004667500795561301, 'solver': 'lbfgs'})</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (25,), 'activation': 'tanh', 'solver': 'lbfgs', 'alpha': 0.004595404869695763, 'batch_size': 16, 'learning_rate': 'adaptive', 'learning_rate_init': 0.017267304977364763}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (20,), 'activation': 'logistic', 'solver': 'lbfgs', 'alpha': np.float64(0.013222789474460183), 'batch_size': 8, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.0016815235903728416)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (25,), 'activation': 'logistic', 'solver': 'lbfgs', 'alpha': np.float64(0.023381919093715474), 'batch_size': 16, 'learning_rate': 'constant', 'learning_rate_init': np.float64(0.0036985387846246013)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (20,), 'activation': 'tanh', 'solver': 'lbfgs', 'alpha': np.float64(0.008981709303673896), 'batch_size': 8, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.1)}</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (20,), 'activation': 'tanh', 'solver': 'lbfgs', 'alpha': np.float64(0.09973052206276951), 'batch_size': 8, 'learning_rate': 'adaptive', 'learning_rate_init': np.float64(0.030376529765923272)}</t>
+  </si>
+  <si>
+    <t>Run time (seconds)</t>
+  </si>
+  <si>
+    <t>Best hyperparmaeters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -148,13 +315,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,591 +646,1592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B8A25C-4AAE-4DDC-AEEC-3A82A3DAE577}">
-  <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="2" customWidth="1"/>
-    <col min="2" max="7" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="23.5703125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.85546875" style="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B3" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.99865651589789495</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.99867662296706705</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.998652753770087</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2527.7157085819999</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="5">
+        <v>4658.777167792</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="5">
+        <v>58258.0994284509</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.99910434393193004</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.99915038232795195</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.99910179303509405</v>
+      </c>
+      <c r="L4" s="5">
+        <v>523.11330422799904</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="5">
+        <v>216.67339086299901</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1915.9380834860001</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2120.9121261830001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1643.4085285799999</v>
+      </c>
+      <c r="O5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1479.75887313199</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>0.99820868786385997</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.99815864820087097</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.99820392418034398</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>206.68089662999901</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="5">
+        <v>80.958212367000598</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="5">
+        <v>470.51018771900198</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.99910434393193004</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.99915038232795195</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.99910179303509405</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1539.4592071489999</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1680.95666740199</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="5">
+        <v>11559.4107153859</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.99910434393193004</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.99910187829304498</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.99910187829304498</v>
+      </c>
+      <c r="L8" s="5">
+        <v>720.65306308900097</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2425.05804024799</v>
+      </c>
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="5">
+        <v>5740.6481165589903</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>730.90037004599901</v>
+      </c>
+      <c r="M9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1446.49708280299</v>
+      </c>
+      <c r="O9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="5">
+        <v>12207.2387348589</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.99776085982982499</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.99773178064871004</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.99775480093540203</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.99910434393193004</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.99910187829304498</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.99910187829304498</v>
+      </c>
+      <c r="L10" s="5">
+        <v>749.513500972001</v>
+      </c>
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2470.9796398919998</v>
+      </c>
+      <c r="O10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10016.754617373899</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="L13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.99132947976878605</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.99149404165274502</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.98692622950819597</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.98843930635838095</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.946957671957672</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.96632374792365905</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>36.925676605082103</v>
+      </c>
+      <c r="M15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="5">
+        <v>841.44755251996605</v>
+      </c>
+      <c r="O15" t="s">
+        <v>64</v>
+      </c>
+      <c r="P15" s="5">
+        <v>5897.038746192</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.98699421965317902</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.97031601439496096</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.96269990709754805</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.989884393063583</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.96385017421602703</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.97659637611875705</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>7.3190095119643903</v>
+      </c>
+      <c r="M16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="5">
+        <v>32.475106819067101</v>
+      </c>
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="5">
+        <v>108.855607041041</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.99132947976878605</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.99149404165274502</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.98692622950819597</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.96098265895953705</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.64059405940594005</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.67422191691378497</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1670.2541506730399</v>
+      </c>
+      <c r="M17" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1624.83819222496</v>
+      </c>
+      <c r="O17" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" s="5">
+        <v>507.97311167500402</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.99277456647398798</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.99034728213977496</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.97977245219075204</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.96387283236994203</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.89444444444444404</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.71055509413067497</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="J18" s="6">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5">
+        <v>10.9370861250208</v>
+      </c>
+      <c r="M18" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="5">
+        <v>6.8793270790483803</v>
+      </c>
+      <c r="O18" t="s">
+        <v>67</v>
+      </c>
+      <c r="P18" s="5">
+        <v>49.400379798957097</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.989884393063583</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.98814120242691605</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.98481716686837895</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.98554913294797597</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.95567226890756296</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.95304199527469902</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6">
+        <v>1</v>
+      </c>
+      <c r="J19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>247.41406421200301</v>
+      </c>
+      <c r="M19" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" s="5">
+        <v>226.17018845700599</v>
+      </c>
+      <c r="O19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P19" s="5">
+        <v>1279.785964765</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.99132947976878605</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.99149404165274502</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.98692622950819597</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.97687861271676302</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.90675197231361204</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.90662974666183904</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6">
+        <v>1</v>
+      </c>
+      <c r="J20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5">
+        <v>214.94819244707401</v>
+      </c>
+      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="5">
+        <v>110.534520688001</v>
+      </c>
+      <c r="O20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P20" s="5">
+        <v>949.65055221505395</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.989884393063583</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.98814120242691605</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.98481716686837895</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.98554913294797597</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.95567226890756296</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.95304199527469902</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5">
+        <v>328.15564276510798</v>
+      </c>
+      <c r="M21" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="5">
+        <v>171.589216334978</v>
+      </c>
+      <c r="O21" t="s">
+        <v>68</v>
+      </c>
+      <c r="P21" s="5">
+        <v>2328.29035659995</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0.989884393063583</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.98814120242691605</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.98481716686837895</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.97687861271676302</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.90675197231361204</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0.90662974666183904</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5">
+        <v>154.81823111698</v>
+      </c>
+      <c r="M22" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="5">
+        <v>123.68916558101699</v>
+      </c>
+      <c r="O22" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1997.0289967870301</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>9</v>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H25:J25"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{315CF2D0-6DAF-4879-8FFF-A79C62AA1C9F}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="2" customWidth="1"/>
-    <col min="2" max="7" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="8" max="8" width="33.85546875" customWidth="1"/>
+    <col min="9" max="9" width="36.140625" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+      <c r="B1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
+        <v>2527.7157085819999</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4658.777167792</v>
+      </c>
+      <c r="D3" s="5">
+        <v>58258.0994284509</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
+        <v>523.11330422799904</v>
+      </c>
+      <c r="C4" s="5">
+        <v>216.67339086299901</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1915.9380834860001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2120.9121261830001</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1643.4085285799999</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1479.75887313199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
+        <v>206.68089662999901</v>
+      </c>
+      <c r="C6" s="5">
+        <v>80.958212367000598</v>
+      </c>
+      <c r="D6" s="5">
+        <v>470.51018771900198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1539.4592071489999</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1680.95666740199</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11559.4107153859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5">
+        <v>720.65306308900097</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2425.05804024799</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5740.6481165589903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5">
+        <v>730.90037004599901</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1446.49708280299</v>
+      </c>
+      <c r="D9" s="5">
+        <v>12207.2387348589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5">
+        <v>749.513500972001</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2470.9796398919998</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10016.754617373899</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G14" s="7"/>
+      <c r="H14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="G15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="G17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="G21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="8.85546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>9</v>
       </c>
     </row>
